--- a/events/RioDeJaneiro_2018_WCH/RioDeJaneiro_2018_WCH_start.xlsx
+++ b/events/RioDeJaneiro_2018_WCH/RioDeJaneiro_2018_WCH_start.xlsx
@@ -31397,11 +31397,6 @@
           <t>MACKIC Dusan</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
-        <is>
-          <t>72217</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -47212,11 +47207,6 @@
       <c r="R760" t="inlineStr">
         <is>
           <t>MACKIC Dusan</t>
-        </is>
-      </c>
-      <c r="U760" t="inlineStr">
-        <is>
-          <t>72217</t>
         </is>
       </c>
     </row>

--- a/events/RioDeJaneiro_2018_WCH/RioDeJaneiro_2018_WCH_start.xlsx
+++ b/events/RioDeJaneiro_2018_WCH/RioDeJaneiro_2018_WCH_start.xlsx
@@ -1333,6 +1333,11 @@
           <t>42027</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30205,6 +30210,11 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>37267</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -32657,6 +32667,11 @@
           <t>35079</t>
         </is>
       </c>
+      <c r="Y521" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -32851,6 +32866,11 @@
           <t>JANE Jakub</t>
         </is>
       </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
       <c r="Y524" t="inlineStr">
         <is>
           <t>35061</t>
@@ -33241,6 +33261,11 @@
           <t>35079</t>
         </is>
       </c>
+      <c r="Y529" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -33387,6 +33412,11 @@
           <t>JANE Jakub</t>
         </is>
       </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
       <c r="Y531" t="inlineStr">
         <is>
           <t>35061</t>
@@ -45755,6 +45785,11 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
+      <c r="X737" t="inlineStr">
+        <is>
+          <t>37267</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -48835,6 +48870,11 @@
       <c r="R786" t="inlineStr">
         <is>
           <t>VALIKOVA Barbora</t>
+        </is>
+      </c>
+      <c r="X786" t="inlineStr">
+        <is>
+          <t>37267</t>
         </is>
       </c>
     </row>
